--- a/data/data_components.xlsx
+++ b/data/data_components.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhiyuanzhang/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhiyuanzhang/Documents/GitHub/vhPPIpredict-viral-phenotypes/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1531A64-A9F1-B24B-9818-A97A386B173D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D44FD238-9379-B841-966B-E7DAA49C0F99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29580" yWindow="1860" windowWidth="27000" windowHeight="16400" xr2:uid="{68185579-3BCF-3E40-9734-EBBDF42F89D0}"/>
+    <workbookView xWindow="45780" yWindow="5020" windowWidth="27000" windowHeight="16400" xr2:uid="{68185579-3BCF-3E40-9734-EBBDF42F89D0}"/>
   </bookViews>
   <sheets>
     <sheet name="data_components" sheetId="1" r:id="rId1"/>
@@ -102,35 +102,35 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>Infectivity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>no human-to-human</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>limited human-to-human</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sustained human-to-human</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Annotation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Merge into Other</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>high level</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>low level</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Infectivity</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>no human-to-human</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>limited human-to-human</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sustained human-to-human</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Annotation</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Merge into Other</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -564,7 +564,7 @@
         <v>11</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="19">
@@ -633,7 +633,7 @@
         <v>12</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="19">
@@ -647,7 +647,7 @@
         <v>7</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="19">
@@ -661,7 +661,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="19">
@@ -713,7 +713,7 @@
         <v>17</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C14" s="2">
         <v>59</v>
@@ -724,18 +724,18 @@
         <v>17</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C15" s="1">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="19">
       <c r="A16" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C16" s="1">
         <v>123</v>
@@ -743,10 +743,10 @@
     </row>
     <row r="17" spans="1:3" ht="19">
       <c r="A17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="C17" s="1">
         <v>31</v>
@@ -754,10 +754,10 @@
     </row>
     <row r="18" spans="1:3" ht="20" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C18" s="1">
         <v>60</v>
